--- a/tools/importer/reports/import-magazine-listing.report.xlsx
+++ b/tools/importer/reports/import-magazine-listing.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-08T21:34:42.021Z</t>
+    <t>2026-09-09T00:42:46.429Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
@@ -73,7 +73,7 @@
     <t>grid-landing</t>
   </si>
   <si>
-    <t>2026-09-08T22:26:10.145Z</t>
+    <t>2026-09-09T00:20:15.285Z</t>
   </si>
   <si>
     <t>About Us</t>
@@ -136,7 +136,7 @@
     <t>magazine-listing</t>
   </si>
   <si>
-    <t>2026-09-08T23:17:16.145Z</t>
+    <t>2026-09-09T00:42:52.237Z</t>
   </si>
   <si>
     <t>Magazine</t>
@@ -157,7 +157,7 @@
     <t>adventure-detail</t>
   </si>
   <si>
-    <t>2026-09-08T21:54:09.673Z</t>
+    <t>2026-09-09T00:39:02.787Z</t>
   </si>
   <si>
     <t>Bali Surf Camp</t>
@@ -172,7 +172,7 @@
     <t>us/en/adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-09-08T23:13:38.399Z</t>
+    <t>2026-09-09T00:34:17.437Z</t>
   </si>
   <si>
     <t>Beervana in Portland</t>
@@ -187,7 +187,7 @@
     <t>us/en/adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-09-08T23:13:43.595Z</t>
+    <t>2026-09-09T00:34:24.478Z</t>
   </si>
   <si>
     <t>Climbing New Zealand</t>
@@ -202,7 +202,7 @@
     <t>us/en/adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-09-08T23:13:47.662Z</t>
+    <t>2026-09-09T00:34:28.586Z</t>
   </si>
   <si>
     <t>Colorado Rock Climbing</t>
@@ -217,7 +217,7 @@
     <t>us/en/adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-09-08T23:13:53.124Z</t>
+    <t>2026-09-09T00:34:33.705Z</t>
   </si>
   <si>
     <t>Cycling Southern Utah</t>
@@ -232,7 +232,7 @@
     <t>us/en/adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-09-08T23:13:58.684Z</t>
+    <t>2026-09-09T00:34:39.423Z</t>
   </si>
   <si>
     <t>Cycling Tuscany</t>
@@ -247,7 +247,7 @@
     <t>us/en/adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-09-08T23:14:03.351Z</t>
+    <t>2026-09-09T00:34:44.102Z</t>
   </si>
   <si>
     <t>Downhill Skiing Wyoming</t>
@@ -262,7 +262,7 @@
     <t>us/en/adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-09-08T23:14:09.355Z</t>
+    <t>2026-09-09T00:34:49.753Z</t>
   </si>
   <si>
     <t>Gastronomic Marais Tour</t>
@@ -277,7 +277,7 @@
     <t>us/en/adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-09-08T23:14:14.479Z</t>
+    <t>2026-09-09T00:34:53.487Z</t>
   </si>
   <si>
     <t>Napa Wine Tasting</t>
@@ -292,7 +292,7 @@
     <t>us/en/adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-09-08T23:14:21.206Z</t>
+    <t>2026-09-09T00:34:58.434Z</t>
   </si>
   <si>
     <t>Riverside Camping</t>
@@ -307,7 +307,7 @@
     <t>us/en/adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-09-08T23:14:25.832Z</t>
+    <t>2026-09-09T00:35:04.436Z</t>
   </si>
   <si>
     <t>Ski Touring Mont Blanc</t>
@@ -322,7 +322,7 @@
     <t>us/en/adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-09-08T23:14:31.096Z</t>
+    <t>2026-09-09T00:35:10.824Z</t>
   </si>
   <si>
     <t>Surf Camp in Costa Rica</t>
@@ -337,7 +337,7 @@
     <t>us/en/adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-09-08T23:14:37.318Z</t>
+    <t>2026-09-09T00:35:16.900Z</t>
   </si>
   <si>
     <t>Tahoe Skiing</t>
@@ -352,7 +352,7 @@
     <t>us/en/adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-09-08T23:14:42.145Z</t>
+    <t>2026-09-09T00:35:21.919Z</t>
   </si>
   <si>
     <t>West Coast Cycling</t>
@@ -367,7 +367,7 @@
     <t>us/en/adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-09-08T23:14:46.514Z</t>
+    <t>2026-09-09T00:35:28.659Z</t>
   </si>
   <si>
     <t>Whistler Mountain Biking</t>
@@ -382,7 +382,7 @@
     <t>us/en/adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-09-08T23:14:51.390Z</t>
+    <t>2026-09-09T00:35:35.568Z</t>
   </si>
   <si>
     <t>Yosemite Backpacking</t>
@@ -403,7 +403,7 @@
     <t>article-detail</t>
   </si>
   <si>
-    <t>2026-09-08T22:17:11.757Z</t>
+    <t>2026-09-09T00:35:40.594Z</t>
   </si>
   <si>
     <t>Arctic Surfing</t>
@@ -418,7 +418,7 @@
     <t>us/en/magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-09-08T23:15:30.514Z</t>
+    <t>2026-09-09T00:35:45.497Z</t>
   </si>
   <si>
     <t>Ultimate Guide to LA Skateparks</t>
@@ -433,7 +433,7 @@
     <t>us/en/magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-09-08T23:15:35.185Z</t>
+    <t>2026-09-09T00:35:50.886Z</t>
   </si>
   <si>
     <t>San Diego Surf Spots</t>
@@ -448,7 +448,7 @@
     <t>us/en/magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-09-08T23:15:39.980Z</t>
+    <t>2026-09-09T00:35:57.010Z</t>
   </si>
   <si>
     <t>Ski Touring</t>
@@ -463,7 +463,7 @@
     <t>us/en/magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-09-08T23:15:44.581Z</t>
+    <t>2026-09-09T00:36:03.009Z</t>
   </si>
   <si>
     <t>Western Australia</t>
